--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Obj.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Obj.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="613">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1841,6 +1841,27 @@
   </si>
   <si>
     <t xml:space="preserve">サツマイーモ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">꽃밭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flower field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">花畑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152</t>
   </si>
 </sst>
 </file>
@@ -2069,7 +2090,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="16.15"/>
@@ -4649,6 +4670,57 @@
       </c>
       <c r="E152" s="0" t="s">
         <v>605</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="0" t="s">
+        <v>606</v>
+      </c>
+      <c r="B153" s="0" t="s">
+        <v>607</v>
+      </c>
+      <c r="C153" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="D153" s="0" t="s">
+        <v>609</v>
+      </c>
+      <c r="E153" s="0" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="B154" s="0" t="s">
+        <v>607</v>
+      </c>
+      <c r="C154" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="D154" s="0" t="s">
+        <v>609</v>
+      </c>
+      <c r="E154" s="0" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="0" t="s">
+        <v>612</v>
+      </c>
+      <c r="B155" s="0" t="s">
+        <v>607</v>
+      </c>
+      <c r="C155" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D155" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="E155" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
